--- a/data/trans_orig/P32E$bar_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023</t>
+          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11321</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>68,49%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14978</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24597</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15241</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>35627</t>
+          <t>36089</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25320</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8624</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31886</t>
+          <t>31133</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13263</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>807</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8868</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>29949</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>42399</t>
+          <t>42857</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>28297</t>
+          <t>27402</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>43485</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>531</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>23269</t>
+          <t>24128</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>82776</t>
+          <t>83638</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>106876</t>
+          <t>108288</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>32177</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>45948</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>122822</t>
+          <t>122849</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>149033</t>
+          <t>150025</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>87186</t>
+          <t>87956</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>78322</t>
+          <t>79562</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>107576</t>
+          <t>109730</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23355</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>46973</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>58588</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>40750</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>25652</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>51410</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32E$bar_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -1294,27 +1294,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1364,27 +1364,27 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15271</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -2545,27 +2545,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14601</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3071,27 +3071,27 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>849</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3184,27 +3184,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>21136</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24631</t>
+          <t>24757</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,27 +3605,27 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20947</t>
+          <t>22176</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>31434</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>17810</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>19676</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>38931</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>29138</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>36089</t>
+          <t>46571</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25011</t>
+          <t>33173</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>23677</t>
+          <t>32494</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>41832</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19233</t>
+          <t>27344</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>43,02%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>29949</t>
+          <t>33268</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>38970</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>42857</t>
+          <t>47736</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19779</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>40541</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>48709</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,67%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>18785</t>
+          <t>20859</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>22156</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>26240</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>83638</t>
+          <t>91893</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>108288</t>
+          <t>117638</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>46314</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>37657</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>136649</t>
+          <t>152399</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>122849</t>
+          <t>137276</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>150025</t>
+          <t>166546</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>87085</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>62476</t>
+          <t>72468</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>87956</t>
+          <t>100652</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>109790</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>79562</t>
+          <t>92920</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>109730</t>
+          <t>126553</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>53549</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>32587</t>
+          <t>39074</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>58588</t>
+          <t>70110</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>40750</t>
+          <t>41745</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>53671</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -5729,32 +5729,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
